--- a/src/components/Roster/sanction.xlsx
+++ b/src/components/Roster/sanction.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MYPRO\Roster\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MYPRO\pzhr_web\src\components\Roster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC254D7-B6C5-4100-8FFA-CB8FCB12ECF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FFB851-C9C7-4E91-A25D-31A3833E20EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{97B97223-865E-45D4-9E75-2997D7267C15}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{97B97223-865E-45D4-9E75-2997D7267C15}"/>
   </bookViews>
   <sheets>
     <sheet name="III" sheetId="1" r:id="rId1"/>
     <sheet name="IV" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">III!$A$1:$P$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">IV!$A$1:$P$49</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -205,7 +206,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -253,13 +254,6 @@
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color rgb="FF7030A0"/>
       <name val="Times New Roman"/>
@@ -280,7 +274,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -289,18 +283,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -337,19 +325,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -367,7 +342,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -385,38 +360,14 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -427,17 +378,10 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -445,27 +389,20 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -474,10 +411,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -833,26 +780,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F914DD-9CA0-4F58-9507-29CB9EFA06D1}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:P49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="13.85546875" customWidth="1"/>
     <col min="3" max="3" width="38.85546875" customWidth="1"/>
-    <col min="4" max="4" width="45.42578125" customWidth="1"/>
+    <col min="4" max="4" width="37.85546875" customWidth="1"/>
     <col min="16" max="16" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:16" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="14" t="s">
         <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -888,7 +836,7 @@
       <c r="O1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="6" t="s">
         <v>11</v>
       </c>
     </row>
@@ -986,7 +934,7 @@
         <v>3</v>
       </c>
       <c r="P3" s="3">
-        <f>SUM(E3:O3)</f>
+        <f t="shared" ref="P3:P49" si="0">SUM(E3:O3)</f>
         <v>9</v>
       </c>
     </row>
@@ -1035,6 +983,7 @@
         <v>9</v>
       </c>
       <c r="P4" s="3">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
@@ -1083,6 +1032,7 @@
         <v>1</v>
       </c>
       <c r="P5" s="3">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -1119,7 +1069,7 @@
         <v>1</v>
       </c>
       <c r="L6" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
@@ -1131,7 +1081,8 @@
         <v>19</v>
       </c>
       <c r="P6" s="3">
-        <v>39</v>
+        <f t="shared" si="0"/>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
@@ -1179,6 +1130,7 @@
         <v>2</v>
       </c>
       <c r="P7" s="3">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
@@ -1227,6 +1179,7 @@
         <v>3</v>
       </c>
       <c r="P8" s="3">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
@@ -1275,6 +1228,7 @@
         <v>23</v>
       </c>
       <c r="P9" s="3">
+        <f t="shared" si="0"/>
         <v>57</v>
       </c>
     </row>
@@ -1323,6 +1277,7 @@
         <v>3</v>
       </c>
       <c r="P10" s="3">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
@@ -1371,10 +1326,11 @@
         <v>5</v>
       </c>
       <c r="P11" s="3">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
@@ -1418,11 +1374,12 @@
       <c r="O12" s="5">
         <v>17</v>
       </c>
-      <c r="P12" s="6">
+      <c r="P12" s="3">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>17</v>
       </c>
@@ -1466,11 +1423,12 @@
       <c r="O13" s="5">
         <v>90</v>
       </c>
-      <c r="P13" s="6">
+      <c r="P13" s="3">
+        <f t="shared" si="0"/>
         <v>137</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
@@ -1514,11 +1472,12 @@
       <c r="O14" s="5">
         <v>30</v>
       </c>
-      <c r="P14" s="6">
+      <c r="P14" s="3">
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
@@ -1562,11 +1521,12 @@
       <c r="O15" s="5">
         <v>31</v>
       </c>
-      <c r="P15" s="6">
+      <c r="P15" s="3">
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>17</v>
       </c>
@@ -1610,11 +1570,12 @@
       <c r="O16" s="5">
         <v>107</v>
       </c>
-      <c r="P16" s="6">
+      <c r="P16" s="3">
+        <f t="shared" si="0"/>
         <v>273</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="1.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>17</v>
       </c>
@@ -1659,10 +1620,11 @@
         <v>4</v>
       </c>
       <c r="P17" s="3">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>29</v>
       </c>
@@ -1707,10 +1669,11 @@
         <v>29</v>
       </c>
       <c r="P18" s="3">
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>29</v>
       </c>
@@ -1755,10 +1718,11 @@
         <v>2</v>
       </c>
       <c r="P19" s="3">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>29</v>
       </c>
@@ -1803,10 +1767,11 @@
         <v>8</v>
       </c>
       <c r="P20" s="3">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>29</v>
       </c>
@@ -1851,10 +1816,11 @@
         <v>1</v>
       </c>
       <c r="P21" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>29</v>
       </c>
@@ -1866,19 +1832,19 @@
         <v>21</v>
       </c>
       <c r="E22" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F22" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G22" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="5">
         <v>1</v>
       </c>
       <c r="I22" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" s="5">
         <v>1</v>
@@ -1887,22 +1853,23 @@
         <v>1</v>
       </c>
       <c r="L22" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M22" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N22" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O22" s="5">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="P22" s="3">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+        <f t="shared" ref="P22:P24" si="1">SUM(E22:O22)</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>29</v>
       </c>
@@ -1923,7 +1890,7 @@
         <v>1</v>
       </c>
       <c r="H23" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="5">
         <v>0</v>
@@ -1935,22 +1902,23 @@
         <v>0</v>
       </c>
       <c r="L23" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M23" s="5">
         <v>1</v>
       </c>
       <c r="N23" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P23" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>29</v>
       </c>
@@ -1962,7 +1930,7 @@
         <v>22</v>
       </c>
       <c r="E24" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" s="5">
         <v>1</v>
@@ -1992,13 +1960,14 @@
         <v>0</v>
       </c>
       <c r="O24" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P24" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>29</v>
       </c>
@@ -2010,19 +1979,19 @@
         <v>21</v>
       </c>
       <c r="E25" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F25" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G25" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" s="5">
         <v>1</v>
       </c>
       <c r="I25" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" s="5">
         <v>1</v>
@@ -2031,22 +2000,23 @@
         <v>1</v>
       </c>
       <c r="L25" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M25" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N25" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O25" s="5">
-        <v>15</v>
-      </c>
-      <c r="P25" s="8">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="P25" s="3">
+        <f>SUM(E25:O25)</f>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>29</v>
       </c>
@@ -2067,7 +2037,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="5">
         <v>0</v>
@@ -2079,22 +2049,23 @@
         <v>0</v>
       </c>
       <c r="L26" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" s="5">
         <v>1</v>
       </c>
       <c r="N26" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P26" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+        <f>SUM(E26:O26)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>29</v>
       </c>
@@ -2106,7 +2077,7 @@
         <v>22</v>
       </c>
       <c r="E27" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="5">
         <v>1</v>
@@ -2136,13 +2107,14 @@
         <v>0</v>
       </c>
       <c r="O27" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P27" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="20.25" x14ac:dyDescent="0.3">
+        <f>SUM(E27:O27)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>29</v>
       </c>
@@ -2151,7 +2123,7 @@
         <v>25</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E28" s="5">
         <v>3</v>
@@ -2186,11 +2158,12 @@
       <c r="O28" s="5">
         <v>15</v>
       </c>
-      <c r="P28" s="6">
+      <c r="P28" s="3">
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>29</v>
       </c>
@@ -2199,46 +2172,47 @@
         <v>20</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E29" s="5">
+        <v>38</v>
+      </c>
+      <c r="E29" s="23">
         <v>15</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="23">
         <v>8</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="23">
         <v>4</v>
       </c>
-      <c r="H29" s="5">
-        <v>3</v>
-      </c>
-      <c r="I29" s="5">
+      <c r="H29" s="23">
+        <v>3</v>
+      </c>
+      <c r="I29" s="23">
         <v>4</v>
       </c>
-      <c r="J29" s="5">
-        <v>2</v>
-      </c>
-      <c r="K29" s="5">
-        <v>2</v>
-      </c>
-      <c r="L29" s="5">
-        <v>0</v>
-      </c>
-      <c r="M29" s="5">
-        <v>0</v>
-      </c>
-      <c r="N29" s="5">
-        <v>0</v>
-      </c>
-      <c r="O29" s="5">
+      <c r="J29" s="23">
+        <v>2</v>
+      </c>
+      <c r="K29" s="23">
+        <v>2</v>
+      </c>
+      <c r="L29" s="23">
+        <v>0</v>
+      </c>
+      <c r="M29" s="23">
+        <v>0</v>
+      </c>
+      <c r="N29" s="23">
+        <v>0</v>
+      </c>
+      <c r="O29" s="23">
         <v>79</v>
       </c>
-      <c r="P29" s="6">
+      <c r="P29" s="24">
+        <f>SUM(E29:O29)</f>
         <v>117</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>29</v>
       </c>
@@ -2247,7 +2221,7 @@
         <v>18</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E30" s="5">
         <v>6</v>
@@ -2282,11 +2256,12 @@
       <c r="O30" s="5">
         <v>30</v>
       </c>
-      <c r="P30" s="6">
+      <c r="P30" s="3">
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>29</v>
       </c>
@@ -2295,7 +2270,7 @@
         <v>19</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E31" s="5">
         <v>6</v>
@@ -2330,11 +2305,12 @@
       <c r="O31" s="5">
         <v>30</v>
       </c>
-      <c r="P31" s="14">
+      <c r="P31" s="3">
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>29</v>
       </c>
@@ -2378,11 +2354,12 @@
       <c r="O32" s="5">
         <v>106</v>
       </c>
-      <c r="P32" s="14">
+      <c r="P32" s="3">
+        <f t="shared" si="0"/>
         <v>270</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>29</v>
       </c>
@@ -2426,11 +2403,12 @@
       <c r="O33" s="5">
         <v>2</v>
       </c>
-      <c r="P33" s="14">
+      <c r="P33" s="3">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>30</v>
       </c>
@@ -2474,11 +2452,12 @@
       <c r="O34" s="5">
         <v>26</v>
       </c>
-      <c r="P34" s="11">
+      <c r="P34" s="3">
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>30</v>
       </c>
@@ -2522,11 +2501,12 @@
       <c r="O35" s="5">
         <v>2</v>
       </c>
-      <c r="P35" s="11">
+      <c r="P35" s="3">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>30</v>
       </c>
@@ -2570,11 +2550,12 @@
       <c r="O36" s="5">
         <v>6</v>
       </c>
-      <c r="P36" s="11">
+      <c r="P36" s="3">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>30</v>
       </c>
@@ -2618,11 +2599,12 @@
       <c r="O37" s="5">
         <v>1</v>
       </c>
-      <c r="P37" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="P37" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>30</v>
       </c>
@@ -2633,44 +2615,45 @@
       <c r="D38" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E38" s="5">
-        <v>6</v>
-      </c>
-      <c r="F38" s="5">
+      <c r="E38" s="7">
+        <v>3</v>
+      </c>
+      <c r="F38" s="7">
+        <v>2</v>
+      </c>
+      <c r="G38" s="7">
+        <v>1</v>
+      </c>
+      <c r="H38" s="7">
+        <v>1</v>
+      </c>
+      <c r="I38" s="7">
+        <v>1</v>
+      </c>
+      <c r="J38" s="7">
+        <v>1</v>
+      </c>
+      <c r="K38" s="5">
+        <v>0</v>
+      </c>
+      <c r="L38" s="5">
         <v>4</v>
       </c>
-      <c r="G38" s="5">
-        <v>1</v>
-      </c>
-      <c r="H38" s="5">
-        <v>1</v>
-      </c>
-      <c r="I38" s="5">
-        <v>2</v>
-      </c>
-      <c r="J38" s="5">
-        <v>1</v>
-      </c>
-      <c r="K38" s="5">
-        <v>1</v>
-      </c>
-      <c r="L38" s="5">
-        <v>9</v>
-      </c>
       <c r="M38" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N38" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O38" s="5">
-        <v>18</v>
-      </c>
-      <c r="P38" s="11">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="P38" s="25">
+        <f>SUM(E38:O38)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>30</v>
       </c>
@@ -2682,7 +2665,7 @@
         <v>14</v>
       </c>
       <c r="E39" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" s="5">
         <v>1</v>
@@ -2703,22 +2686,23 @@
         <v>0</v>
       </c>
       <c r="L39" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M39" s="5">
         <v>1</v>
       </c>
       <c r="N39" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" s="5">
-        <v>3</v>
-      </c>
-      <c r="P39" s="11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="P39" s="25">
+        <f>SUM(E39:O39)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>30</v>
       </c>
@@ -2733,7 +2717,7 @@
         <v>1</v>
       </c>
       <c r="F40" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" s="5">
         <v>0</v>
@@ -2760,13 +2744,14 @@
         <v>0</v>
       </c>
       <c r="O40" s="5">
-        <v>4</v>
-      </c>
-      <c r="P40" s="11">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="P40" s="25">
+        <f>SUM(E40:O40)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>30</v>
       </c>
@@ -2777,44 +2762,45 @@
       <c r="D41" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E41" s="9">
-        <v>3</v>
-      </c>
-      <c r="F41" s="10">
-        <v>2</v>
-      </c>
-      <c r="G41" s="10">
-        <v>1</v>
-      </c>
-      <c r="H41" s="10">
-        <v>1</v>
-      </c>
-      <c r="I41" s="10">
-        <v>1</v>
-      </c>
-      <c r="J41" s="10">
+      <c r="E41" s="5">
+        <v>6</v>
+      </c>
+      <c r="F41" s="5">
+        <v>4</v>
+      </c>
+      <c r="G41" s="5">
+        <v>1</v>
+      </c>
+      <c r="H41" s="5">
+        <v>1</v>
+      </c>
+      <c r="I41" s="5">
+        <v>2</v>
+      </c>
+      <c r="J41" s="5">
         <v>1</v>
       </c>
       <c r="K41" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M41" s="5">
         <v>2</v>
       </c>
       <c r="N41" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O41" s="5">
-        <v>7</v>
-      </c>
-      <c r="P41" s="11">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="P41" s="3">
+        <f>SUM(E41:O41)</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>30</v>
       </c>
@@ -2825,8 +2811,8 @@
       <c r="D42" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E42" s="12">
-        <v>0</v>
+      <c r="E42" s="5">
+        <v>1</v>
       </c>
       <c r="F42" s="5">
         <v>1</v>
@@ -2847,22 +2833,23 @@
         <v>0</v>
       </c>
       <c r="L42" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M42" s="5">
         <v>1</v>
       </c>
       <c r="N42" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" s="5">
-        <v>1</v>
-      </c>
-      <c r="P42" s="11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="P42" s="3">
+        <f>SUM(E42:O42)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>30</v>
       </c>
@@ -2873,11 +2860,11 @@
       <c r="D43" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E43" s="12">
+      <c r="E43" s="5">
         <v>1</v>
       </c>
       <c r="F43" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" s="5">
         <v>0</v>
@@ -2904,13 +2891,14 @@
         <v>0</v>
       </c>
       <c r="O43" s="5">
-        <v>2</v>
-      </c>
-      <c r="P43" s="11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" ht="20.25" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3">
+        <f>SUM(E43:O43)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>30</v>
       </c>
@@ -2954,11 +2942,12 @@
       <c r="O44" s="5">
         <v>15</v>
       </c>
-      <c r="P44" s="14">
+      <c r="P44" s="3">
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>30</v>
       </c>
@@ -3002,11 +2991,12 @@
       <c r="O45" s="5">
         <v>61</v>
       </c>
-      <c r="P45" s="14">
+      <c r="P45" s="3">
+        <f t="shared" si="0"/>
         <v>91</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>30</v>
       </c>
@@ -3050,11 +3040,12 @@
       <c r="O46" s="5">
         <v>25</v>
       </c>
-      <c r="P46" s="14">
+      <c r="P46" s="3">
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>30</v>
       </c>
@@ -3098,11 +3089,12 @@
       <c r="O47" s="5">
         <v>25</v>
       </c>
-      <c r="P47" s="14">
+      <c r="P47" s="3">
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>30</v>
       </c>
@@ -3146,11 +3138,12 @@
       <c r="O48" s="5">
         <v>80</v>
       </c>
-      <c r="P48" s="14">
+      <c r="P48" s="3">
+        <f t="shared" si="0"/>
         <v>225</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:16" ht="23.25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>30</v>
       </c>
@@ -3161,44 +3154,52 @@
       <c r="D49" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E49" s="13">
-        <v>1</v>
-      </c>
-      <c r="F49" s="13">
-        <v>1</v>
-      </c>
-      <c r="G49" s="13">
-        <v>0</v>
-      </c>
-      <c r="H49" s="13">
-        <v>0</v>
-      </c>
-      <c r="I49" s="13">
-        <v>0</v>
-      </c>
-      <c r="J49" s="13">
-        <v>0</v>
-      </c>
-      <c r="K49" s="13">
-        <v>0</v>
-      </c>
-      <c r="L49" s="13">
-        <v>0</v>
-      </c>
-      <c r="M49" s="13">
-        <v>0</v>
-      </c>
-      <c r="N49" s="13">
-        <v>0</v>
-      </c>
-      <c r="O49" s="13">
+      <c r="E49" s="8">
+        <v>1</v>
+      </c>
+      <c r="F49" s="8">
+        <v>1</v>
+      </c>
+      <c r="G49" s="8">
+        <v>0</v>
+      </c>
+      <c r="H49" s="8">
+        <v>0</v>
+      </c>
+      <c r="I49" s="8">
+        <v>0</v>
+      </c>
+      <c r="J49" s="8">
+        <v>0</v>
+      </c>
+      <c r="K49" s="8">
+        <v>0</v>
+      </c>
+      <c r="L49" s="8">
+        <v>0</v>
+      </c>
+      <c r="M49" s="8">
+        <v>0</v>
+      </c>
+      <c r="N49" s="8">
+        <v>0</v>
+      </c>
+      <c r="O49" s="8">
         <v>5</v>
       </c>
-      <c r="P49" s="15">
+      <c r="P49" s="3">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P49" xr:uid="{52F914DD-9CA0-4F58-9507-29CB9EFA06D1}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="RPUC"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3206,71 +3207,72 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF36A4E-756E-480F-94E4-598988175605}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:P49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" style="31" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" style="20" customWidth="1"/>
     <col min="2" max="2" width="31.140625" customWidth="1"/>
     <col min="3" max="3" width="28.42578125" customWidth="1"/>
-    <col min="4" max="4" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.28515625" customWidth="1"/>
     <col min="5" max="16" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="33" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:16" s="22" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="7" t="s">
+      <c r="E1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="16" t="s">
         <v>32</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -3312,15 +3314,16 @@
       <c r="O2" s="5">
         <v>3</v>
       </c>
-      <c r="P2" s="7">
+      <c r="P2" s="3">
+        <f>SUM(E2:O2)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="16" t="s">
         <v>33</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -3362,15 +3365,16 @@
       <c r="O3" s="5">
         <v>4</v>
       </c>
-      <c r="P3" s="7">
+      <c r="P3" s="3">
+        <f t="shared" ref="P3:P49" si="0">SUM(E3:O3)</f>
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="16" t="s">
         <v>34</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -3412,15 +3416,16 @@
       <c r="O4" s="5">
         <v>4</v>
       </c>
-      <c r="P4" s="7">
+      <c r="P4" s="3">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="16" t="s">
         <v>35</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -3462,15 +3467,16 @@
       <c r="O5" s="5">
         <v>4</v>
       </c>
-      <c r="P5" s="7">
+      <c r="P5" s="3">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="17" t="s">
         <v>36</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -3512,7 +3518,8 @@
       <c r="O6" s="5">
         <v>3</v>
       </c>
-      <c r="P6" s="7">
+      <c r="P6" s="3">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
@@ -3520,7 +3527,7 @@
       <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="15" t="s">
         <v>39</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -3562,7 +3569,8 @@
       <c r="O7" s="5">
         <v>4</v>
       </c>
-      <c r="P7" s="7">
+      <c r="P7" s="3">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
     </row>
@@ -3570,7 +3578,7 @@
       <c r="A8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="15" t="s">
         <v>40</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -3612,7 +3620,8 @@
       <c r="O8" s="5">
         <v>4</v>
       </c>
-      <c r="P8" s="7">
+      <c r="P8" s="3">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
     </row>
@@ -3620,7 +3629,7 @@
       <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="15" t="s">
         <v>41</v>
       </c>
       <c r="C9" s="4" t="s">
@@ -3662,7 +3671,8 @@
       <c r="O9" s="5">
         <v>3</v>
       </c>
-      <c r="P9" s="7">
+      <c r="P9" s="3">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
@@ -3670,7 +3680,7 @@
       <c r="A10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="15" t="s">
         <v>42</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -3712,15 +3722,16 @@
       <c r="O10" s="5">
         <v>3</v>
       </c>
-      <c r="P10" s="7">
+      <c r="P10" s="3">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="21" t="s">
         <v>45</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -3762,15 +3773,16 @@
       <c r="O11" s="5">
         <v>0</v>
       </c>
-      <c r="P11" s="29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="P11" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="21" t="s">
         <v>46</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -3812,15 +3824,16 @@
       <c r="O12" s="5">
         <v>0</v>
       </c>
-      <c r="P12" s="29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="P12" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="21" t="s">
         <v>43</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -3829,44 +3842,45 @@
       <c r="D13" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="28">
-        <v>1</v>
-      </c>
-      <c r="F13" s="28">
-        <v>0</v>
-      </c>
-      <c r="G13" s="28">
-        <v>1</v>
-      </c>
-      <c r="H13" s="28">
-        <v>0</v>
-      </c>
-      <c r="I13" s="28">
-        <v>0</v>
-      </c>
-      <c r="J13" s="28">
-        <v>0</v>
-      </c>
-      <c r="K13" s="28">
-        <v>0</v>
-      </c>
-      <c r="L13" s="28">
-        <v>0</v>
-      </c>
-      <c r="M13" s="28">
-        <v>0</v>
-      </c>
-      <c r="N13" s="28">
-        <v>0</v>
-      </c>
-      <c r="O13" s="28">
-        <v>1</v>
-      </c>
-      <c r="P13" s="19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E13" s="18">
+        <v>1</v>
+      </c>
+      <c r="F13" s="18">
+        <v>0</v>
+      </c>
+      <c r="G13" s="18">
+        <v>1</v>
+      </c>
+      <c r="H13" s="18">
+        <v>0</v>
+      </c>
+      <c r="I13" s="18">
+        <v>0</v>
+      </c>
+      <c r="J13" s="18">
+        <v>0</v>
+      </c>
+      <c r="K13" s="18">
+        <v>0</v>
+      </c>
+      <c r="L13" s="18">
+        <v>0</v>
+      </c>
+      <c r="M13" s="18">
+        <v>0</v>
+      </c>
+      <c r="N13" s="18">
+        <v>0</v>
+      </c>
+      <c r="O13" s="18">
+        <v>1</v>
+      </c>
+      <c r="P13" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
@@ -3879,44 +3893,45 @@
       <c r="D14" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="17">
-        <v>3</v>
-      </c>
-      <c r="F14" s="17">
-        <v>2</v>
-      </c>
-      <c r="G14" s="17">
-        <v>0</v>
-      </c>
-      <c r="H14" s="17">
-        <v>0</v>
-      </c>
-      <c r="I14" s="17">
-        <v>1</v>
-      </c>
-      <c r="J14" s="17">
-        <v>1</v>
-      </c>
-      <c r="K14" s="17">
-        <v>1</v>
-      </c>
-      <c r="L14" s="17">
+      <c r="E14" s="10">
+        <v>3</v>
+      </c>
+      <c r="F14" s="10">
+        <v>2</v>
+      </c>
+      <c r="G14" s="10">
+        <v>0</v>
+      </c>
+      <c r="H14" s="10">
+        <v>0</v>
+      </c>
+      <c r="I14" s="10">
+        <v>1</v>
+      </c>
+      <c r="J14" s="10">
+        <v>1</v>
+      </c>
+      <c r="K14" s="10">
+        <v>1</v>
+      </c>
+      <c r="L14" s="10">
         <v>4</v>
       </c>
-      <c r="M14" s="17">
-        <v>2</v>
-      </c>
-      <c r="N14" s="17">
-        <v>2</v>
-      </c>
-      <c r="O14" s="17">
+      <c r="M14" s="10">
+        <v>2</v>
+      </c>
+      <c r="N14" s="10">
+        <v>2</v>
+      </c>
+      <c r="O14" s="10">
         <v>6</v>
       </c>
-      <c r="P14" s="7">
+      <c r="P14" s="3">
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
@@ -3929,44 +3944,45 @@
       <c r="D15" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="17">
-        <v>0</v>
-      </c>
-      <c r="F15" s="17">
-        <v>1</v>
-      </c>
-      <c r="G15" s="17">
-        <v>1</v>
-      </c>
-      <c r="H15" s="17">
-        <v>0</v>
-      </c>
-      <c r="I15" s="17">
-        <v>0</v>
-      </c>
-      <c r="J15" s="17">
-        <v>0</v>
-      </c>
-      <c r="K15" s="17">
-        <v>0</v>
-      </c>
-      <c r="L15" s="17">
-        <v>1</v>
-      </c>
-      <c r="M15" s="17">
-        <v>1</v>
-      </c>
-      <c r="N15" s="17">
-        <v>0</v>
-      </c>
-      <c r="O15" s="17">
-        <v>1</v>
-      </c>
-      <c r="P15" s="7">
+      <c r="E15" s="10">
+        <v>0</v>
+      </c>
+      <c r="F15" s="10">
+        <v>1</v>
+      </c>
+      <c r="G15" s="10">
+        <v>1</v>
+      </c>
+      <c r="H15" s="10">
+        <v>0</v>
+      </c>
+      <c r="I15" s="10">
+        <v>0</v>
+      </c>
+      <c r="J15" s="10">
+        <v>0</v>
+      </c>
+      <c r="K15" s="10">
+        <v>0</v>
+      </c>
+      <c r="L15" s="10">
+        <v>1</v>
+      </c>
+      <c r="M15" s="10">
+        <v>1</v>
+      </c>
+      <c r="N15" s="10">
+        <v>0</v>
+      </c>
+      <c r="O15" s="10">
+        <v>1</v>
+      </c>
+      <c r="P15" s="3">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>17</v>
       </c>
@@ -3979,44 +3995,45 @@
       <c r="D16" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="17">
-        <v>0</v>
-      </c>
-      <c r="F16" s="17">
-        <v>1</v>
-      </c>
-      <c r="G16" s="17">
-        <v>0</v>
-      </c>
-      <c r="H16" s="17">
-        <v>0</v>
-      </c>
-      <c r="I16" s="17">
-        <v>1</v>
-      </c>
-      <c r="J16" s="17">
-        <v>0</v>
-      </c>
-      <c r="K16" s="17">
-        <v>0</v>
-      </c>
-      <c r="L16" s="17">
-        <v>1</v>
-      </c>
-      <c r="M16" s="17">
-        <v>1</v>
-      </c>
-      <c r="N16" s="17">
-        <v>0</v>
-      </c>
-      <c r="O16" s="17">
-        <v>1</v>
-      </c>
-      <c r="P16" s="7">
+      <c r="E16" s="10">
+        <v>0</v>
+      </c>
+      <c r="F16" s="10">
+        <v>1</v>
+      </c>
+      <c r="G16" s="10">
+        <v>0</v>
+      </c>
+      <c r="H16" s="10">
+        <v>0</v>
+      </c>
+      <c r="I16" s="10">
+        <v>1</v>
+      </c>
+      <c r="J16" s="10">
+        <v>0</v>
+      </c>
+      <c r="K16" s="10">
+        <v>0</v>
+      </c>
+      <c r="L16" s="10">
+        <v>1</v>
+      </c>
+      <c r="M16" s="10">
+        <v>1</v>
+      </c>
+      <c r="N16" s="10">
+        <v>0</v>
+      </c>
+      <c r="O16" s="10">
+        <v>1</v>
+      </c>
+      <c r="P16" s="3">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>17</v>
       </c>
@@ -4029,48 +4046,49 @@
       <c r="D17" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="17">
-        <v>1</v>
-      </c>
-      <c r="F17" s="17">
-        <v>0</v>
-      </c>
-      <c r="G17" s="17">
-        <v>1</v>
-      </c>
-      <c r="H17" s="17">
-        <v>0</v>
-      </c>
-      <c r="I17" s="17">
-        <v>0</v>
-      </c>
-      <c r="J17" s="17">
-        <v>0</v>
-      </c>
-      <c r="K17" s="17">
-        <v>0</v>
-      </c>
-      <c r="L17" s="17">
-        <v>1</v>
-      </c>
-      <c r="M17" s="17">
-        <v>1</v>
-      </c>
-      <c r="N17" s="17">
-        <v>0</v>
-      </c>
-      <c r="O17" s="17">
-        <v>1</v>
-      </c>
-      <c r="P17" s="7">
+      <c r="E17" s="10">
+        <v>1</v>
+      </c>
+      <c r="F17" s="10">
+        <v>0</v>
+      </c>
+      <c r="G17" s="10">
+        <v>1</v>
+      </c>
+      <c r="H17" s="10">
+        <v>0</v>
+      </c>
+      <c r="I17" s="10">
+        <v>0</v>
+      </c>
+      <c r="J17" s="10">
+        <v>0</v>
+      </c>
+      <c r="K17" s="10">
+        <v>0</v>
+      </c>
+      <c r="L17" s="10">
+        <v>1</v>
+      </c>
+      <c r="M17" s="10">
+        <v>1</v>
+      </c>
+      <c r="N17" s="10">
+        <v>0</v>
+      </c>
+      <c r="O17" s="10">
+        <v>1</v>
+      </c>
+      <c r="P17" s="3">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C18" s="4" t="s">
@@ -4079,44 +4097,45 @@
       <c r="D18" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="17">
-        <v>0</v>
-      </c>
-      <c r="F18" s="17">
-        <v>1</v>
-      </c>
-      <c r="G18" s="17">
-        <v>1</v>
-      </c>
-      <c r="H18" s="17">
-        <v>0</v>
-      </c>
-      <c r="I18" s="17">
-        <v>0</v>
-      </c>
-      <c r="J18" s="17">
-        <v>0</v>
-      </c>
-      <c r="K18" s="17">
-        <v>0</v>
-      </c>
-      <c r="L18" s="17">
-        <v>1</v>
-      </c>
-      <c r="M18" s="17">
-        <v>1</v>
-      </c>
-      <c r="N18" s="17">
-        <v>0</v>
-      </c>
-      <c r="O18" s="17">
-        <v>1</v>
-      </c>
-      <c r="P18" s="7">
+      <c r="E18" s="10">
+        <v>0</v>
+      </c>
+      <c r="F18" s="10">
+        <v>1</v>
+      </c>
+      <c r="G18" s="10">
+        <v>1</v>
+      </c>
+      <c r="H18" s="10">
+        <v>0</v>
+      </c>
+      <c r="I18" s="10">
+        <v>0</v>
+      </c>
+      <c r="J18" s="10">
+        <v>0</v>
+      </c>
+      <c r="K18" s="10">
+        <v>0</v>
+      </c>
+      <c r="L18" s="10">
+        <v>1</v>
+      </c>
+      <c r="M18" s="10">
+        <v>1</v>
+      </c>
+      <c r="N18" s="10">
+        <v>0</v>
+      </c>
+      <c r="O18" s="10">
+        <v>1</v>
+      </c>
+      <c r="P18" s="3">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>29</v>
       </c>
@@ -4129,44 +4148,45 @@
       <c r="D19" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="17">
-        <v>1</v>
-      </c>
-      <c r="F19" s="17">
-        <v>1</v>
-      </c>
-      <c r="G19" s="17">
-        <v>1</v>
-      </c>
-      <c r="H19" s="17">
-        <v>0</v>
-      </c>
-      <c r="I19" s="17">
-        <v>0</v>
-      </c>
-      <c r="J19" s="17">
-        <v>0</v>
-      </c>
-      <c r="K19" s="17">
-        <v>0</v>
-      </c>
-      <c r="L19" s="17">
-        <v>1</v>
-      </c>
-      <c r="M19" s="17">
-        <v>0</v>
-      </c>
-      <c r="N19" s="17">
-        <v>1</v>
-      </c>
-      <c r="O19" s="17">
-        <v>2</v>
-      </c>
-      <c r="P19" s="7">
+      <c r="E19" s="10">
+        <v>1</v>
+      </c>
+      <c r="F19" s="10">
+        <v>1</v>
+      </c>
+      <c r="G19" s="10">
+        <v>1</v>
+      </c>
+      <c r="H19" s="10">
+        <v>0</v>
+      </c>
+      <c r="I19" s="10">
+        <v>0</v>
+      </c>
+      <c r="J19" s="10">
+        <v>0</v>
+      </c>
+      <c r="K19" s="10">
+        <v>0</v>
+      </c>
+      <c r="L19" s="10">
+        <v>1</v>
+      </c>
+      <c r="M19" s="10">
+        <v>0</v>
+      </c>
+      <c r="N19" s="10">
+        <v>1</v>
+      </c>
+      <c r="O19" s="10">
+        <v>2</v>
+      </c>
+      <c r="P19" s="3">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>29</v>
       </c>
@@ -4179,44 +4199,45 @@
       <c r="D20" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E20" s="17">
-        <v>0</v>
-      </c>
-      <c r="F20" s="17">
-        <v>1</v>
-      </c>
-      <c r="G20" s="17">
-        <v>0</v>
-      </c>
-      <c r="H20" s="17">
-        <v>1</v>
-      </c>
-      <c r="I20" s="17">
-        <v>0</v>
-      </c>
-      <c r="J20" s="17">
-        <v>0</v>
-      </c>
-      <c r="K20" s="17">
-        <v>0</v>
-      </c>
-      <c r="L20" s="17">
-        <v>1</v>
-      </c>
-      <c r="M20" s="17">
-        <v>1</v>
-      </c>
-      <c r="N20" s="17">
-        <v>0</v>
-      </c>
-      <c r="O20" s="17">
-        <v>2</v>
-      </c>
-      <c r="P20" s="7">
+      <c r="E20" s="10">
+        <v>0</v>
+      </c>
+      <c r="F20" s="10">
+        <v>1</v>
+      </c>
+      <c r="G20" s="10">
+        <v>0</v>
+      </c>
+      <c r="H20" s="10">
+        <v>1</v>
+      </c>
+      <c r="I20" s="10">
+        <v>0</v>
+      </c>
+      <c r="J20" s="10">
+        <v>0</v>
+      </c>
+      <c r="K20" s="10">
+        <v>0</v>
+      </c>
+      <c r="L20" s="10">
+        <v>1</v>
+      </c>
+      <c r="M20" s="10">
+        <v>1</v>
+      </c>
+      <c r="N20" s="10">
+        <v>0</v>
+      </c>
+      <c r="O20" s="10">
+        <v>2</v>
+      </c>
+      <c r="P20" s="3">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>29</v>
       </c>
@@ -4229,44 +4250,45 @@
       <c r="D21" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="17">
-        <v>1</v>
-      </c>
-      <c r="F21" s="17">
-        <v>0</v>
-      </c>
-      <c r="G21" s="17">
-        <v>1</v>
-      </c>
-      <c r="H21" s="17">
-        <v>0</v>
-      </c>
-      <c r="I21" s="17">
-        <v>0</v>
-      </c>
-      <c r="J21" s="17">
-        <v>0</v>
-      </c>
-      <c r="K21" s="17">
-        <v>0</v>
-      </c>
-      <c r="L21" s="17">
-        <v>1</v>
-      </c>
-      <c r="M21" s="17">
-        <v>1</v>
-      </c>
-      <c r="N21" s="17">
-        <v>0</v>
-      </c>
-      <c r="O21" s="17">
-        <v>1</v>
-      </c>
-      <c r="P21" s="7">
+      <c r="E21" s="10">
+        <v>1</v>
+      </c>
+      <c r="F21" s="10">
+        <v>0</v>
+      </c>
+      <c r="G21" s="10">
+        <v>1</v>
+      </c>
+      <c r="H21" s="10">
+        <v>0</v>
+      </c>
+      <c r="I21" s="10">
+        <v>0</v>
+      </c>
+      <c r="J21" s="10">
+        <v>0</v>
+      </c>
+      <c r="K21" s="10">
+        <v>0</v>
+      </c>
+      <c r="L21" s="10">
+        <v>1</v>
+      </c>
+      <c r="M21" s="10">
+        <v>1</v>
+      </c>
+      <c r="N21" s="10">
+        <v>0</v>
+      </c>
+      <c r="O21" s="10">
+        <v>1</v>
+      </c>
+      <c r="P21" s="3">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>29</v>
       </c>
@@ -4279,48 +4301,49 @@
       <c r="D22" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E22" s="17">
-        <v>2</v>
-      </c>
-      <c r="F22" s="17">
-        <v>1</v>
-      </c>
-      <c r="G22" s="17">
-        <v>1</v>
-      </c>
-      <c r="H22" s="17">
-        <v>0</v>
-      </c>
-      <c r="I22" s="17">
-        <v>0</v>
-      </c>
-      <c r="J22" s="17">
-        <v>1</v>
-      </c>
-      <c r="K22" s="17">
-        <v>0</v>
-      </c>
-      <c r="L22" s="17">
-        <v>3</v>
-      </c>
-      <c r="M22" s="17">
-        <v>2</v>
-      </c>
-      <c r="N22" s="17">
-        <v>2</v>
-      </c>
-      <c r="O22" s="17">
+      <c r="E22" s="10">
+        <v>2</v>
+      </c>
+      <c r="F22" s="10">
+        <v>1</v>
+      </c>
+      <c r="G22" s="10">
+        <v>1</v>
+      </c>
+      <c r="H22" s="10">
+        <v>0</v>
+      </c>
+      <c r="I22" s="10">
+        <v>0</v>
+      </c>
+      <c r="J22" s="10">
+        <v>1</v>
+      </c>
+      <c r="K22" s="10">
+        <v>0</v>
+      </c>
+      <c r="L22" s="10">
+        <v>3</v>
+      </c>
+      <c r="M22" s="10">
+        <v>2</v>
+      </c>
+      <c r="N22" s="10">
+        <v>2</v>
+      </c>
+      <c r="O22" s="10">
         <v>5</v>
       </c>
-      <c r="P22" s="7">
+      <c r="P22" s="3">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="11" t="s">
         <v>45</v>
       </c>
       <c r="C23" s="4" t="s">
@@ -4329,48 +4352,49 @@
       <c r="D23" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E23" s="10">
-        <v>1</v>
-      </c>
-      <c r="F23" s="10">
-        <v>1</v>
-      </c>
-      <c r="G23" s="10">
-        <v>1</v>
-      </c>
-      <c r="H23" s="10">
-        <v>0</v>
-      </c>
-      <c r="I23" s="10">
-        <v>0</v>
-      </c>
-      <c r="J23" s="10">
-        <v>0</v>
-      </c>
-      <c r="K23" s="10">
-        <v>0</v>
-      </c>
-      <c r="L23" s="10">
-        <v>1</v>
-      </c>
-      <c r="M23" s="10">
-        <v>1</v>
-      </c>
-      <c r="N23" s="10">
-        <v>0</v>
-      </c>
-      <c r="O23" s="10">
-        <v>2</v>
-      </c>
-      <c r="P23" s="20">
+      <c r="E23" s="7">
+        <v>1</v>
+      </c>
+      <c r="F23" s="7">
+        <v>1</v>
+      </c>
+      <c r="G23" s="7">
+        <v>1</v>
+      </c>
+      <c r="H23" s="7">
+        <v>0</v>
+      </c>
+      <c r="I23" s="7">
+        <v>0</v>
+      </c>
+      <c r="J23" s="7">
+        <v>0</v>
+      </c>
+      <c r="K23" s="7">
+        <v>0</v>
+      </c>
+      <c r="L23" s="7">
+        <v>1</v>
+      </c>
+      <c r="M23" s="7">
+        <v>1</v>
+      </c>
+      <c r="N23" s="7">
+        <v>0</v>
+      </c>
+      <c r="O23" s="7">
+        <v>2</v>
+      </c>
+      <c r="P23" s="3">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="11" t="s">
         <v>46</v>
       </c>
       <c r="C24" s="4" t="s">
@@ -4379,48 +4403,49 @@
       <c r="D24" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="21">
-        <v>1</v>
-      </c>
-      <c r="F24" s="21">
-        <v>1</v>
-      </c>
-      <c r="G24" s="21">
-        <v>0</v>
-      </c>
-      <c r="H24" s="21">
-        <v>1</v>
-      </c>
-      <c r="I24" s="21">
-        <v>0</v>
-      </c>
-      <c r="J24" s="21">
-        <v>0</v>
-      </c>
-      <c r="K24" s="21">
-        <v>0</v>
-      </c>
-      <c r="L24" s="21">
-        <v>1</v>
-      </c>
-      <c r="M24" s="21">
-        <v>1</v>
-      </c>
-      <c r="N24" s="21">
-        <v>1</v>
-      </c>
-      <c r="O24" s="21">
-        <v>2</v>
-      </c>
-      <c r="P24" s="20">
+      <c r="E24" s="12">
+        <v>1</v>
+      </c>
+      <c r="F24" s="12">
+        <v>1</v>
+      </c>
+      <c r="G24" s="12">
+        <v>0</v>
+      </c>
+      <c r="H24" s="12">
+        <v>1</v>
+      </c>
+      <c r="I24" s="12">
+        <v>0</v>
+      </c>
+      <c r="J24" s="12">
+        <v>0</v>
+      </c>
+      <c r="K24" s="12">
+        <v>0</v>
+      </c>
+      <c r="L24" s="12">
+        <v>1</v>
+      </c>
+      <c r="M24" s="12">
+        <v>1</v>
+      </c>
+      <c r="N24" s="12">
+        <v>1</v>
+      </c>
+      <c r="O24" s="12">
+        <v>2</v>
+      </c>
+      <c r="P24" s="3">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="11" t="s">
         <v>47</v>
       </c>
       <c r="C25" s="4" t="s">
@@ -4429,1245 +4454,1276 @@
       <c r="D25" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E25" s="21">
-        <v>1</v>
-      </c>
-      <c r="F25" s="21">
-        <v>1</v>
-      </c>
-      <c r="G25" s="21">
-        <v>1</v>
-      </c>
-      <c r="H25" s="21">
-        <v>1</v>
-      </c>
-      <c r="I25" s="21">
-        <v>0</v>
-      </c>
-      <c r="J25" s="21">
-        <v>0</v>
-      </c>
-      <c r="K25" s="21">
-        <v>0</v>
-      </c>
-      <c r="L25" s="21">
-        <v>2</v>
-      </c>
-      <c r="M25" s="21">
-        <v>1</v>
-      </c>
-      <c r="N25" s="21">
-        <v>1</v>
-      </c>
-      <c r="O25" s="21">
-        <v>3</v>
-      </c>
-      <c r="P25" s="20">
+      <c r="E25" s="12">
+        <v>1</v>
+      </c>
+      <c r="F25" s="12">
+        <v>1</v>
+      </c>
+      <c r="G25" s="12">
+        <v>1</v>
+      </c>
+      <c r="H25" s="12">
+        <v>1</v>
+      </c>
+      <c r="I25" s="12">
+        <v>0</v>
+      </c>
+      <c r="J25" s="12">
+        <v>0</v>
+      </c>
+      <c r="K25" s="12">
+        <v>0</v>
+      </c>
+      <c r="L25" s="12">
+        <v>2</v>
+      </c>
+      <c r="M25" s="12">
+        <v>1</v>
+      </c>
+      <c r="N25" s="12">
+        <v>1</v>
+      </c>
+      <c r="O25" s="12">
+        <v>3</v>
+      </c>
+      <c r="P25" s="3">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="11" t="s">
         <v>48</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="10">
         <v>10</v>
       </c>
-      <c r="F26" s="17">
+      <c r="F26" s="10">
         <v>6</v>
       </c>
-      <c r="G26" s="17">
-        <v>2</v>
-      </c>
-      <c r="H26" s="17">
-        <v>2</v>
-      </c>
-      <c r="I26" s="17">
-        <v>3</v>
-      </c>
-      <c r="J26" s="17">
-        <v>1</v>
-      </c>
-      <c r="K26" s="17">
-        <v>1</v>
-      </c>
-      <c r="L26" s="17">
-        <v>0</v>
-      </c>
-      <c r="M26" s="17">
-        <v>0</v>
-      </c>
-      <c r="N26" s="17">
-        <v>0</v>
-      </c>
-      <c r="O26" s="17">
+      <c r="G26" s="10">
+        <v>2</v>
+      </c>
+      <c r="H26" s="10">
+        <v>2</v>
+      </c>
+      <c r="I26" s="10">
+        <v>3</v>
+      </c>
+      <c r="J26" s="10">
+        <v>1</v>
+      </c>
+      <c r="K26" s="10">
+        <v>1</v>
+      </c>
+      <c r="L26" s="10">
+        <v>0</v>
+      </c>
+      <c r="M26" s="10">
+        <v>0</v>
+      </c>
+      <c r="N26" s="10">
+        <v>0</v>
+      </c>
+      <c r="O26" s="10">
         <v>51</v>
       </c>
-      <c r="P26" s="7">
+      <c r="P26" s="3">
+        <f t="shared" si="0"/>
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="11" t="s">
         <v>48</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E27" s="17">
+      <c r="E27" s="10">
         <v>10</v>
       </c>
-      <c r="F27" s="17">
+      <c r="F27" s="10">
         <v>6</v>
       </c>
-      <c r="G27" s="17">
-        <v>2</v>
-      </c>
-      <c r="H27" s="17">
-        <v>2</v>
-      </c>
-      <c r="I27" s="17">
-        <v>3</v>
-      </c>
-      <c r="J27" s="17">
-        <v>2</v>
-      </c>
-      <c r="K27" s="17">
-        <v>1</v>
-      </c>
-      <c r="L27" s="17">
-        <v>0</v>
-      </c>
-      <c r="M27" s="17">
-        <v>0</v>
-      </c>
-      <c r="N27" s="17">
-        <v>0</v>
-      </c>
-      <c r="O27" s="17">
+      <c r="G27" s="10">
+        <v>2</v>
+      </c>
+      <c r="H27" s="10">
+        <v>2</v>
+      </c>
+      <c r="I27" s="10">
+        <v>3</v>
+      </c>
+      <c r="J27" s="10">
+        <v>2</v>
+      </c>
+      <c r="K27" s="10">
+        <v>1</v>
+      </c>
+      <c r="L27" s="10">
+        <v>0</v>
+      </c>
+      <c r="M27" s="10">
+        <v>0</v>
+      </c>
+      <c r="N27" s="10">
+        <v>0</v>
+      </c>
+      <c r="O27" s="10">
         <v>54</v>
       </c>
-      <c r="P27" s="7">
+      <c r="P27" s="3">
+        <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="11" t="s">
         <v>48</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E28" s="17">
+      <c r="E28" s="10">
         <v>11</v>
       </c>
-      <c r="F28" s="17">
+      <c r="F28" s="10">
         <v>6</v>
       </c>
-      <c r="G28" s="17">
-        <v>2</v>
-      </c>
-      <c r="H28" s="17">
-        <v>2</v>
-      </c>
-      <c r="I28" s="17">
-        <v>3</v>
-      </c>
-      <c r="J28" s="17">
-        <v>2</v>
-      </c>
-      <c r="K28" s="17">
-        <v>1</v>
-      </c>
-      <c r="L28" s="17">
-        <v>0</v>
-      </c>
-      <c r="M28" s="17">
-        <v>0</v>
-      </c>
-      <c r="N28" s="17">
-        <v>0</v>
-      </c>
-      <c r="O28" s="17">
+      <c r="G28" s="10">
+        <v>2</v>
+      </c>
+      <c r="H28" s="10">
+        <v>2</v>
+      </c>
+      <c r="I28" s="10">
+        <v>3</v>
+      </c>
+      <c r="J28" s="10">
+        <v>2</v>
+      </c>
+      <c r="K28" s="10">
+        <v>1</v>
+      </c>
+      <c r="L28" s="10">
+        <v>0</v>
+      </c>
+      <c r="M28" s="10">
+        <v>0</v>
+      </c>
+      <c r="N28" s="10">
+        <v>0</v>
+      </c>
+      <c r="O28" s="10">
         <v>54</v>
       </c>
-      <c r="P28" s="7">
+      <c r="P28" s="3">
+        <f t="shared" si="0"/>
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="11" t="s">
         <v>48</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E29" s="10">
         <v>10</v>
       </c>
-      <c r="F29" s="17">
+      <c r="F29" s="10">
         <v>6</v>
       </c>
-      <c r="G29" s="17">
-        <v>2</v>
-      </c>
-      <c r="H29" s="17">
-        <v>2</v>
-      </c>
-      <c r="I29" s="17">
-        <v>3</v>
-      </c>
-      <c r="J29" s="17">
-        <v>2</v>
-      </c>
-      <c r="K29" s="17">
-        <v>1</v>
-      </c>
-      <c r="L29" s="17">
-        <v>0</v>
-      </c>
-      <c r="M29" s="17">
-        <v>0</v>
-      </c>
-      <c r="N29" s="17">
-        <v>0</v>
-      </c>
-      <c r="O29" s="17">
+      <c r="G29" s="10">
+        <v>2</v>
+      </c>
+      <c r="H29" s="10">
+        <v>2</v>
+      </c>
+      <c r="I29" s="10">
+        <v>3</v>
+      </c>
+      <c r="J29" s="10">
+        <v>2</v>
+      </c>
+      <c r="K29" s="10">
+        <v>1</v>
+      </c>
+      <c r="L29" s="10">
+        <v>0</v>
+      </c>
+      <c r="M29" s="10">
+        <v>0</v>
+      </c>
+      <c r="N29" s="10">
+        <v>0</v>
+      </c>
+      <c r="O29" s="10">
         <v>54</v>
       </c>
-      <c r="P29" s="7">
+      <c r="P29" s="3">
+        <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="11" t="s">
         <v>48</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E30" s="17">
+      <c r="E30" s="10">
         <v>8</v>
       </c>
-      <c r="F30" s="17">
+      <c r="F30" s="10">
         <v>4</v>
       </c>
-      <c r="G30" s="17">
-        <v>2</v>
-      </c>
-      <c r="H30" s="17">
-        <v>2</v>
-      </c>
-      <c r="I30" s="17">
-        <v>3</v>
-      </c>
-      <c r="J30" s="17">
-        <v>1</v>
-      </c>
-      <c r="K30" s="17">
-        <v>1</v>
-      </c>
-      <c r="L30" s="17">
-        <v>0</v>
-      </c>
-      <c r="M30" s="17">
-        <v>0</v>
-      </c>
-      <c r="N30" s="17">
-        <v>0</v>
-      </c>
-      <c r="O30" s="17">
+      <c r="G30" s="10">
+        <v>2</v>
+      </c>
+      <c r="H30" s="10">
+        <v>2</v>
+      </c>
+      <c r="I30" s="10">
+        <v>3</v>
+      </c>
+      <c r="J30" s="10">
+        <v>1</v>
+      </c>
+      <c r="K30" s="10">
+        <v>1</v>
+      </c>
+      <c r="L30" s="10">
+        <v>0</v>
+      </c>
+      <c r="M30" s="10">
+        <v>0</v>
+      </c>
+      <c r="N30" s="10">
+        <v>0</v>
+      </c>
+      <c r="O30" s="10">
         <v>41</v>
       </c>
-      <c r="P30" s="7">
+      <c r="P30" s="3">
+        <f t="shared" si="0"/>
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="11" t="s">
         <v>48</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="10">
         <v>12</v>
       </c>
-      <c r="F31" s="17">
+      <c r="F31" s="10">
         <v>7</v>
       </c>
-      <c r="G31" s="17">
-        <v>3</v>
-      </c>
-      <c r="H31" s="17">
-        <v>2</v>
-      </c>
-      <c r="I31" s="17">
-        <v>3</v>
-      </c>
-      <c r="J31" s="17">
-        <v>2</v>
-      </c>
-      <c r="K31" s="17">
-        <v>2</v>
-      </c>
-      <c r="L31" s="17">
-        <v>0</v>
-      </c>
-      <c r="M31" s="17">
-        <v>0</v>
-      </c>
-      <c r="N31" s="17">
-        <v>0</v>
-      </c>
-      <c r="O31" s="17">
+      <c r="G31" s="10">
+        <v>3</v>
+      </c>
+      <c r="H31" s="10">
+        <v>2</v>
+      </c>
+      <c r="I31" s="10">
+        <v>3</v>
+      </c>
+      <c r="J31" s="10">
+        <v>2</v>
+      </c>
+      <c r="K31" s="10">
+        <v>2</v>
+      </c>
+      <c r="L31" s="10">
+        <v>0</v>
+      </c>
+      <c r="M31" s="10">
+        <v>0</v>
+      </c>
+      <c r="N31" s="10">
+        <v>0</v>
+      </c>
+      <c r="O31" s="10">
         <v>63</v>
       </c>
-      <c r="P31" s="7">
+      <c r="P31" s="3">
+        <f t="shared" si="0"/>
         <v>94</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="11" t="s">
         <v>48</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E32" s="17">
+      <c r="E32" s="10">
         <v>13</v>
       </c>
-      <c r="F32" s="17">
+      <c r="F32" s="10">
         <v>7</v>
       </c>
-      <c r="G32" s="17">
-        <v>3</v>
-      </c>
-      <c r="H32" s="17">
-        <v>2</v>
-      </c>
-      <c r="I32" s="17">
-        <v>3</v>
-      </c>
-      <c r="J32" s="17">
-        <v>2</v>
-      </c>
-      <c r="K32" s="17">
-        <v>2</v>
-      </c>
-      <c r="L32" s="17">
-        <v>0</v>
-      </c>
-      <c r="M32" s="17">
-        <v>0</v>
-      </c>
-      <c r="N32" s="17">
-        <v>0</v>
-      </c>
-      <c r="O32" s="17">
+      <c r="G32" s="10">
+        <v>3</v>
+      </c>
+      <c r="H32" s="10">
+        <v>2</v>
+      </c>
+      <c r="I32" s="10">
+        <v>3</v>
+      </c>
+      <c r="J32" s="10">
+        <v>2</v>
+      </c>
+      <c r="K32" s="10">
+        <v>2</v>
+      </c>
+      <c r="L32" s="10">
+        <v>0</v>
+      </c>
+      <c r="M32" s="10">
+        <v>0</v>
+      </c>
+      <c r="N32" s="10">
+        <v>0</v>
+      </c>
+      <c r="O32" s="10">
         <v>66</v>
       </c>
-      <c r="P32" s="7">
+      <c r="P32" s="3">
+        <f t="shared" si="0"/>
         <v>98</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="11" t="s">
         <v>48</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E33" s="17">
+      <c r="E33" s="10">
         <v>10</v>
       </c>
-      <c r="F33" s="17">
+      <c r="F33" s="10">
         <v>5</v>
       </c>
-      <c r="G33" s="17">
-        <v>2</v>
-      </c>
-      <c r="H33" s="17">
-        <v>2</v>
-      </c>
-      <c r="I33" s="17">
-        <v>3</v>
-      </c>
-      <c r="J33" s="17">
-        <v>1</v>
-      </c>
-      <c r="K33" s="17">
-        <v>1</v>
-      </c>
-      <c r="L33" s="17">
-        <v>0</v>
-      </c>
-      <c r="M33" s="17">
-        <v>0</v>
-      </c>
-      <c r="N33" s="17">
-        <v>0</v>
-      </c>
-      <c r="O33" s="17">
+      <c r="G33" s="10">
+        <v>2</v>
+      </c>
+      <c r="H33" s="10">
+        <v>2</v>
+      </c>
+      <c r="I33" s="10">
+        <v>3</v>
+      </c>
+      <c r="J33" s="10">
+        <v>1</v>
+      </c>
+      <c r="K33" s="10">
+        <v>1</v>
+      </c>
+      <c r="L33" s="10">
+        <v>0</v>
+      </c>
+      <c r="M33" s="10">
+        <v>0</v>
+      </c>
+      <c r="N33" s="10">
+        <v>0</v>
+      </c>
+      <c r="O33" s="10">
         <v>50</v>
       </c>
-      <c r="P33" s="7">
+      <c r="P33" s="3">
+        <f t="shared" si="0"/>
         <v>74</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="11" t="s">
         <v>48</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E34" s="17">
+      <c r="E34" s="10">
         <v>8</v>
       </c>
-      <c r="F34" s="17">
+      <c r="F34" s="10">
         <v>4</v>
       </c>
-      <c r="G34" s="17">
-        <v>2</v>
-      </c>
-      <c r="H34" s="17">
-        <v>2</v>
-      </c>
-      <c r="I34" s="17">
-        <v>2</v>
-      </c>
-      <c r="J34" s="17">
-        <v>1</v>
-      </c>
-      <c r="K34" s="17">
-        <v>1</v>
-      </c>
-      <c r="L34" s="17">
-        <v>0</v>
-      </c>
-      <c r="M34" s="17">
-        <v>0</v>
-      </c>
-      <c r="N34" s="17">
-        <v>0</v>
-      </c>
-      <c r="O34" s="17">
+      <c r="G34" s="10">
+        <v>2</v>
+      </c>
+      <c r="H34" s="10">
+        <v>2</v>
+      </c>
+      <c r="I34" s="10">
+        <v>2</v>
+      </c>
+      <c r="J34" s="10">
+        <v>1</v>
+      </c>
+      <c r="K34" s="10">
+        <v>1</v>
+      </c>
+      <c r="L34" s="10">
+        <v>0</v>
+      </c>
+      <c r="M34" s="10">
+        <v>0</v>
+      </c>
+      <c r="N34" s="10">
+        <v>0</v>
+      </c>
+      <c r="O34" s="10">
         <v>42</v>
       </c>
-      <c r="P34" s="7">
+      <c r="P34" s="3">
+        <f t="shared" si="0"/>
         <v>62</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="11" t="s">
         <v>48</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E35" s="10">
+      <c r="E35" s="7">
         <v>25</v>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="7">
         <v>14</v>
       </c>
-      <c r="G35" s="10">
+      <c r="G35" s="7">
         <v>6</v>
       </c>
-      <c r="H35" s="10">
+      <c r="H35" s="7">
         <v>5</v>
       </c>
-      <c r="I35" s="10">
+      <c r="I35" s="7">
         <v>6</v>
       </c>
-      <c r="J35" s="10">
+      <c r="J35" s="7">
         <v>4</v>
       </c>
-      <c r="K35" s="10">
+      <c r="K35" s="7">
         <v>4</v>
       </c>
-      <c r="L35" s="10">
-        <v>0</v>
-      </c>
-      <c r="M35" s="10">
-        <v>0</v>
-      </c>
-      <c r="N35" s="10">
-        <v>0</v>
-      </c>
-      <c r="O35" s="10">
+      <c r="L35" s="7">
+        <v>0</v>
+      </c>
+      <c r="M35" s="7">
+        <v>0</v>
+      </c>
+      <c r="N35" s="7">
+        <v>0</v>
+      </c>
+      <c r="O35" s="7">
         <v>131</v>
       </c>
-      <c r="P35" s="20">
+      <c r="P35" s="3">
+        <f t="shared" si="0"/>
         <v>195</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="11" t="s">
         <v>48</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="12">
         <v>24</v>
       </c>
-      <c r="F36" s="21">
+      <c r="F36" s="12">
         <v>13</v>
       </c>
-      <c r="G36" s="21">
+      <c r="G36" s="12">
         <v>5</v>
       </c>
-      <c r="H36" s="21">
+      <c r="H36" s="12">
         <v>5</v>
       </c>
-      <c r="I36" s="21">
+      <c r="I36" s="12">
         <v>6</v>
       </c>
-      <c r="J36" s="21">
+      <c r="J36" s="12">
         <v>4</v>
       </c>
-      <c r="K36" s="21">
+      <c r="K36" s="12">
         <v>4</v>
       </c>
-      <c r="L36" s="21">
-        <v>0</v>
-      </c>
-      <c r="M36" s="21">
-        <v>0</v>
-      </c>
-      <c r="N36" s="21">
-        <v>0</v>
-      </c>
-      <c r="O36" s="21">
+      <c r="L36" s="12">
+        <v>0</v>
+      </c>
+      <c r="M36" s="12">
+        <v>0</v>
+      </c>
+      <c r="N36" s="12">
+        <v>0</v>
+      </c>
+      <c r="O36" s="12">
         <v>123</v>
       </c>
-      <c r="P36" s="20">
+      <c r="P36" s="3">
+        <f t="shared" si="0"/>
         <v>184</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B37" s="18" t="s">
+      <c r="B37" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C37" s="18" t="s">
+      <c r="C37" s="11" t="s">
         <v>48</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E37" s="21">
+      <c r="E37" s="12">
         <v>24</v>
       </c>
-      <c r="F37" s="21">
+      <c r="F37" s="12">
         <v>13</v>
       </c>
-      <c r="G37" s="21">
+      <c r="G37" s="12">
         <v>6</v>
       </c>
-      <c r="H37" s="21">
+      <c r="H37" s="12">
         <v>5</v>
       </c>
-      <c r="I37" s="21">
+      <c r="I37" s="12">
         <v>6</v>
       </c>
-      <c r="J37" s="21">
+      <c r="J37" s="12">
         <v>4</v>
       </c>
-      <c r="K37" s="21">
-        <v>3</v>
-      </c>
-      <c r="L37" s="21">
-        <v>0</v>
-      </c>
-      <c r="M37" s="21">
-        <v>0</v>
-      </c>
-      <c r="N37" s="21">
-        <v>0</v>
-      </c>
-      <c r="O37" s="21">
+      <c r="K37" s="12">
+        <v>3</v>
+      </c>
+      <c r="L37" s="12">
+        <v>0</v>
+      </c>
+      <c r="M37" s="12">
+        <v>0</v>
+      </c>
+      <c r="N37" s="12">
+        <v>0</v>
+      </c>
+      <c r="O37" s="12">
         <v>122</v>
       </c>
-      <c r="P37" s="20">
+      <c r="P37" s="3">
+        <f t="shared" si="0"/>
         <v>183</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="C38" s="11" t="s">
         <v>50</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E38" s="22">
+      <c r="E38" s="13">
         <v>21</v>
       </c>
-      <c r="F38" s="22">
+      <c r="F38" s="13">
         <v>11</v>
       </c>
-      <c r="G38" s="22">
+      <c r="G38" s="13">
         <v>5</v>
       </c>
-      <c r="H38" s="22">
+      <c r="H38" s="13">
         <v>4</v>
       </c>
-      <c r="I38" s="22">
+      <c r="I38" s="13">
         <v>6</v>
       </c>
-      <c r="J38" s="22">
-        <v>3</v>
-      </c>
-      <c r="K38" s="22">
-        <v>3</v>
-      </c>
-      <c r="L38" s="22">
+      <c r="J38" s="13">
+        <v>3</v>
+      </c>
+      <c r="K38" s="13">
+        <v>3</v>
+      </c>
+      <c r="L38" s="13">
         <v>30</v>
       </c>
-      <c r="M38" s="22">
+      <c r="M38" s="13">
         <v>10</v>
       </c>
-      <c r="N38" s="22">
+      <c r="N38" s="13">
         <v>10</v>
       </c>
-      <c r="O38" s="22">
+      <c r="O38" s="13">
         <v>57</v>
       </c>
-      <c r="P38" s="23">
+      <c r="P38" s="3">
+        <f t="shared" si="0"/>
         <v>160</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="11" t="s">
         <v>50</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E39" s="22">
+      <c r="E39" s="13">
         <v>17</v>
       </c>
-      <c r="F39" s="22">
+      <c r="F39" s="13">
         <v>9</v>
       </c>
-      <c r="G39" s="22">
+      <c r="G39" s="13">
         <v>4</v>
       </c>
-      <c r="H39" s="22">
-        <v>3</v>
-      </c>
-      <c r="I39" s="22">
+      <c r="H39" s="13">
+        <v>3</v>
+      </c>
+      <c r="I39" s="13">
         <v>5</v>
       </c>
-      <c r="J39" s="22">
-        <v>3</v>
-      </c>
-      <c r="K39" s="22">
-        <v>3</v>
-      </c>
-      <c r="L39" s="22">
+      <c r="J39" s="13">
+        <v>3</v>
+      </c>
+      <c r="K39" s="13">
+        <v>3</v>
+      </c>
+      <c r="L39" s="13">
         <v>25</v>
       </c>
-      <c r="M39" s="22">
+      <c r="M39" s="13">
         <v>5</v>
       </c>
-      <c r="N39" s="22">
+      <c r="N39" s="13">
         <v>5</v>
       </c>
-      <c r="O39" s="22">
+      <c r="O39" s="13">
         <v>52</v>
       </c>
-      <c r="P39" s="23">
+      <c r="P39" s="3">
+        <f t="shared" si="0"/>
         <v>131</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="11" t="s">
         <v>50</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E40" s="22">
+      <c r="E40" s="13">
         <v>19</v>
       </c>
-      <c r="F40" s="22">
+      <c r="F40" s="13">
         <v>10</v>
       </c>
-      <c r="G40" s="22">
+      <c r="G40" s="13">
         <v>4</v>
       </c>
-      <c r="H40" s="22">
+      <c r="H40" s="13">
         <v>4</v>
       </c>
-      <c r="I40" s="22">
+      <c r="I40" s="13">
         <v>5</v>
       </c>
-      <c r="J40" s="22">
-        <v>3</v>
-      </c>
-      <c r="K40" s="22">
-        <v>3</v>
-      </c>
-      <c r="L40" s="22">
+      <c r="J40" s="13">
+        <v>3</v>
+      </c>
+      <c r="K40" s="13">
+        <v>3</v>
+      </c>
+      <c r="L40" s="13">
         <v>28</v>
       </c>
-      <c r="M40" s="22">
+      <c r="M40" s="13">
         <v>10</v>
       </c>
-      <c r="N40" s="22">
+      <c r="N40" s="13">
         <v>10</v>
       </c>
-      <c r="O40" s="22">
+      <c r="O40" s="13">
         <v>51</v>
       </c>
-      <c r="P40" s="23">
+      <c r="P40" s="3">
+        <f t="shared" si="0"/>
         <v>147</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="C41" s="11" t="s">
         <v>50</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E41" s="22">
+      <c r="E41" s="13">
         <v>20</v>
       </c>
-      <c r="F41" s="22">
+      <c r="F41" s="13">
         <v>11</v>
       </c>
-      <c r="G41" s="22">
+      <c r="G41" s="13">
         <v>5</v>
       </c>
-      <c r="H41" s="22">
+      <c r="H41" s="13">
         <v>5</v>
       </c>
-      <c r="I41" s="22">
+      <c r="I41" s="13">
         <v>5</v>
       </c>
-      <c r="J41" s="22">
-        <v>3</v>
-      </c>
-      <c r="K41" s="22">
-        <v>3</v>
-      </c>
-      <c r="L41" s="22">
+      <c r="J41" s="13">
+        <v>3</v>
+      </c>
+      <c r="K41" s="13">
+        <v>3</v>
+      </c>
+      <c r="L41" s="13">
         <v>29</v>
       </c>
-      <c r="M41" s="22">
+      <c r="M41" s="13">
         <v>8</v>
       </c>
-      <c r="N41" s="22">
+      <c r="N41" s="13">
         <v>8</v>
       </c>
-      <c r="O41" s="22">
+      <c r="O41" s="13">
         <v>57</v>
       </c>
-      <c r="P41" s="23">
+      <c r="P41" s="3">
+        <f t="shared" si="0"/>
         <v>154</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="11" t="s">
         <v>50</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E42" s="22">
+      <c r="E42" s="13">
         <v>15</v>
       </c>
-      <c r="F42" s="22">
+      <c r="F42" s="13">
         <v>8</v>
       </c>
-      <c r="G42" s="22">
+      <c r="G42" s="13">
         <v>4</v>
       </c>
-      <c r="H42" s="22">
-        <v>3</v>
-      </c>
-      <c r="I42" s="22">
+      <c r="H42" s="13">
+        <v>3</v>
+      </c>
+      <c r="I42" s="13">
         <v>5</v>
       </c>
-      <c r="J42" s="22">
-        <v>3</v>
-      </c>
-      <c r="K42" s="22">
-        <v>3</v>
-      </c>
-      <c r="L42" s="22">
+      <c r="J42" s="13">
+        <v>3</v>
+      </c>
+      <c r="K42" s="13">
+        <v>3</v>
+      </c>
+      <c r="L42" s="13">
         <v>22</v>
       </c>
-      <c r="M42" s="22">
+      <c r="M42" s="13">
         <v>6</v>
       </c>
-      <c r="N42" s="22">
+      <c r="N42" s="13">
         <v>6</v>
       </c>
-      <c r="O42" s="22">
+      <c r="O42" s="13">
         <v>43</v>
       </c>
-      <c r="P42" s="23">
+      <c r="P42" s="3">
+        <f t="shared" si="0"/>
         <v>118</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="C43" s="11" t="s">
         <v>50</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E43" s="17">
+      <c r="E43" s="10">
         <v>24</v>
       </c>
-      <c r="F43" s="17">
+      <c r="F43" s="10">
         <v>13</v>
       </c>
-      <c r="G43" s="17">
+      <c r="G43" s="10">
         <v>6</v>
       </c>
-      <c r="H43" s="17">
+      <c r="H43" s="10">
         <v>5</v>
       </c>
-      <c r="I43" s="17">
+      <c r="I43" s="10">
         <v>7</v>
       </c>
-      <c r="J43" s="17">
+      <c r="J43" s="10">
         <v>4</v>
       </c>
-      <c r="K43" s="17">
+      <c r="K43" s="10">
         <v>4</v>
       </c>
-      <c r="L43" s="17">
+      <c r="L43" s="10">
         <v>35</v>
       </c>
-      <c r="M43" s="17">
+      <c r="M43" s="10">
         <v>8</v>
       </c>
-      <c r="N43" s="17">
+      <c r="N43" s="10">
         <v>8</v>
       </c>
-      <c r="O43" s="17">
+      <c r="O43" s="10">
         <v>72</v>
       </c>
-      <c r="P43" s="7">
+      <c r="P43" s="3">
+        <f t="shared" si="0"/>
         <v>186</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="11" t="s">
         <v>50</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E44" s="17">
+      <c r="E44" s="10">
         <v>25</v>
       </c>
-      <c r="F44" s="17">
+      <c r="F44" s="10">
         <v>13</v>
       </c>
-      <c r="G44" s="17">
+      <c r="G44" s="10">
         <v>6</v>
       </c>
-      <c r="H44" s="17">
+      <c r="H44" s="10">
         <v>5</v>
       </c>
-      <c r="I44" s="17">
+      <c r="I44" s="10">
         <v>6</v>
       </c>
-      <c r="J44" s="17">
+      <c r="J44" s="10">
         <v>4</v>
       </c>
-      <c r="K44" s="17">
+      <c r="K44" s="10">
         <v>4</v>
       </c>
-      <c r="L44" s="17">
+      <c r="L44" s="10">
         <v>37</v>
       </c>
-      <c r="M44" s="17">
+      <c r="M44" s="10">
         <v>10</v>
       </c>
-      <c r="N44" s="17">
+      <c r="N44" s="10">
         <v>10</v>
       </c>
-      <c r="O44" s="17">
+      <c r="O44" s="10">
         <v>72</v>
       </c>
-      <c r="P44" s="7">
+      <c r="P44" s="3">
+        <f t="shared" si="0"/>
         <v>192</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C45" s="18" t="s">
+      <c r="C45" s="11" t="s">
         <v>50</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E45" s="17">
+      <c r="E45" s="10">
         <v>18</v>
       </c>
-      <c r="F45" s="17">
+      <c r="F45" s="10">
         <v>10</v>
       </c>
-      <c r="G45" s="17">
+      <c r="G45" s="10">
         <v>4</v>
       </c>
-      <c r="H45" s="17">
-        <v>3</v>
-      </c>
-      <c r="I45" s="17">
+      <c r="H45" s="10">
+        <v>3</v>
+      </c>
+      <c r="I45" s="10">
         <v>5</v>
       </c>
-      <c r="J45" s="17">
-        <v>3</v>
-      </c>
-      <c r="K45" s="17">
-        <v>3</v>
-      </c>
-      <c r="L45" s="17">
+      <c r="J45" s="10">
+        <v>3</v>
+      </c>
+      <c r="K45" s="10">
+        <v>3</v>
+      </c>
+      <c r="L45" s="10">
         <v>26</v>
       </c>
-      <c r="M45" s="17">
+      <c r="M45" s="10">
         <v>10</v>
       </c>
-      <c r="N45" s="17">
+      <c r="N45" s="10">
         <v>10</v>
       </c>
-      <c r="O45" s="17">
+      <c r="O45" s="10">
         <v>47</v>
       </c>
-      <c r="P45" s="7">
+      <c r="P45" s="3">
+        <f t="shared" si="0"/>
         <v>139</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="11" t="s">
         <v>50</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E46" s="17">
+      <c r="E46" s="10">
         <v>18</v>
       </c>
-      <c r="F46" s="17">
+      <c r="F46" s="10">
         <v>9</v>
       </c>
-      <c r="G46" s="17">
+      <c r="G46" s="10">
         <v>4</v>
       </c>
-      <c r="H46" s="17">
-        <v>3</v>
-      </c>
-      <c r="I46" s="17">
+      <c r="H46" s="10">
+        <v>3</v>
+      </c>
+      <c r="I46" s="10">
         <v>5</v>
       </c>
-      <c r="J46" s="17">
-        <v>3</v>
-      </c>
-      <c r="K46" s="17">
-        <v>3</v>
-      </c>
-      <c r="L46" s="17">
+      <c r="J46" s="10">
+        <v>3</v>
+      </c>
+      <c r="K46" s="10">
+        <v>3</v>
+      </c>
+      <c r="L46" s="10">
         <v>26</v>
       </c>
-      <c r="M46" s="17">
+      <c r="M46" s="10">
         <v>7</v>
       </c>
-      <c r="N46" s="17">
+      <c r="N46" s="10">
         <v>7</v>
       </c>
-      <c r="O46" s="17">
+      <c r="O46" s="10">
         <v>51</v>
       </c>
-      <c r="P46" s="7">
+      <c r="P46" s="3">
+        <f t="shared" si="0"/>
         <v>136</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B47" s="18" t="s">
+      <c r="B47" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="18" t="s">
+      <c r="C47" s="11" t="s">
         <v>50</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E47" s="10">
+      <c r="E47" s="7">
         <v>19</v>
       </c>
-      <c r="F47" s="10">
+      <c r="F47" s="7">
         <v>10</v>
       </c>
-      <c r="G47" s="10">
+      <c r="G47" s="7">
         <v>4</v>
       </c>
-      <c r="H47" s="10">
+      <c r="H47" s="7">
         <v>4</v>
       </c>
-      <c r="I47" s="10">
+      <c r="I47" s="7">
         <v>5</v>
       </c>
-      <c r="J47" s="10">
-        <v>3</v>
-      </c>
-      <c r="K47" s="10">
-        <v>3</v>
-      </c>
-      <c r="L47" s="10">
+      <c r="J47" s="7">
+        <v>3</v>
+      </c>
+      <c r="K47" s="7">
+        <v>3</v>
+      </c>
+      <c r="L47" s="7">
         <v>27</v>
       </c>
-      <c r="M47" s="10">
+      <c r="M47" s="7">
         <v>11</v>
       </c>
-      <c r="N47" s="10">
+      <c r="N47" s="7">
         <v>11</v>
       </c>
-      <c r="O47" s="10">
+      <c r="O47" s="7">
         <v>48</v>
       </c>
-      <c r="P47" s="20">
+      <c r="P47" s="3">
+        <f t="shared" si="0"/>
         <v>145</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B48" s="18" t="s">
+      <c r="B48" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C48" s="18" t="s">
+      <c r="C48" s="11" t="s">
         <v>50</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E48" s="21">
+      <c r="E48" s="12">
         <v>22</v>
       </c>
-      <c r="F48" s="21">
+      <c r="F48" s="12">
         <v>12</v>
       </c>
-      <c r="G48" s="21">
+      <c r="G48" s="12">
         <v>5</v>
       </c>
-      <c r="H48" s="21">
+      <c r="H48" s="12">
         <v>4</v>
       </c>
-      <c r="I48" s="21">
+      <c r="I48" s="12">
         <v>6</v>
       </c>
-      <c r="J48" s="21">
+      <c r="J48" s="12">
         <v>4</v>
       </c>
-      <c r="K48" s="21">
-        <v>3</v>
-      </c>
-      <c r="L48" s="21">
+      <c r="K48" s="12">
+        <v>3</v>
+      </c>
+      <c r="L48" s="12">
         <v>32</v>
       </c>
-      <c r="M48" s="21">
+      <c r="M48" s="12">
         <v>13</v>
       </c>
-      <c r="N48" s="21">
+      <c r="N48" s="12">
         <v>13</v>
       </c>
-      <c r="O48" s="21">
+      <c r="O48" s="12">
         <v>56</v>
       </c>
-      <c r="P48" s="20">
+      <c r="P48" s="3">
+        <f t="shared" si="0"/>
         <v>170</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B49" s="18" t="s">
+      <c r="B49" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C49" s="18" t="s">
+      <c r="C49" s="11" t="s">
         <v>50</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E49" s="21">
+      <c r="E49" s="12">
         <v>18</v>
       </c>
-      <c r="F49" s="21">
+      <c r="F49" s="12">
         <v>10</v>
       </c>
-      <c r="G49" s="21">
+      <c r="G49" s="12">
         <v>4</v>
       </c>
-      <c r="H49" s="21">
-        <v>3</v>
-      </c>
-      <c r="I49" s="21">
+      <c r="H49" s="12">
+        <v>3</v>
+      </c>
+      <c r="I49" s="12">
         <v>6</v>
       </c>
-      <c r="J49" s="21">
-        <v>3</v>
-      </c>
-      <c r="K49" s="21">
-        <v>3</v>
-      </c>
-      <c r="L49" s="21">
+      <c r="J49" s="12">
+        <v>3</v>
+      </c>
+      <c r="K49" s="12">
+        <v>3</v>
+      </c>
+      <c r="L49" s="12">
         <v>26</v>
       </c>
-      <c r="M49" s="21">
+      <c r="M49" s="12">
         <v>10</v>
       </c>
-      <c r="N49" s="21">
+      <c r="N49" s="12">
         <v>10</v>
       </c>
-      <c r="O49" s="21">
+      <c r="O49" s="12">
         <v>43</v>
       </c>
-      <c r="P49" s="20">
+      <c r="P49" s="3">
+        <f t="shared" si="0"/>
         <v>136</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P49" xr:uid="{AAF36A4E-756E-480F-94E4-598988175605}"/>
+  <autoFilter ref="A1:P49" xr:uid="{AAF36A4E-756E-480F-94E4-598988175605}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="GKUC"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
